--- a/appointment_forms/028_seo_strategy_appointment_form--appointment_forms.xlsx
+++ b/appointment_forms/028_seo_strategy_appointment_form--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>keyword_research</t>
+          <t>keyword research</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>link_building</t>
+          <t>link building</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>content_optimization</t>
+          <t>content optimization</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>local_search</t>
+          <t>local search</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>technical_audit</t>
+          <t>technical audit</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>link_building_setup</t>
+          <t>link building setup</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>keyword_research</t>
+          <t>keyword_strategy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>keyword_research</t>
+          <t>keyword strategy</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>keyword_strategy</t>
+          <t>onpage_optimization</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>keyword_strategy</t>
+          <t>onpage optimization</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>onpage_optimization</t>
+          <t>offpage_optimization</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>onpage_optimization</t>
+          <t>offpage optimization</t>
         </is>
       </c>
     </row>
@@ -1030,46 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>offpage_optimization</t>
+          <t>website_setup</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>offpage_optimization</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>seo_service_request_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>technical_audit</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>technical_audit</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>seo_service_request_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>website_setup</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>website_setup</t>
+          <t>website setup</t>
         </is>
       </c>
     </row>
